--- a/airbnb-pricing/output/preisplan.xlsx
+++ b/airbnb-pricing/output/preisplan.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -964,450 +964,454 @@
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>99</v>
-      </c>
-      <c r="E20" t="n">
-        <v>119</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>MEDICA + COMPAMED 2026</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>MEDICA + COMPAMED 2026 + Tokio Hotel (Konzert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>69</v>
-      </c>
-      <c r="E22" t="n">
-        <v>89</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>89</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
         <v>79</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>99</v>
       </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Deutschland Cup (Eishockey)</t>
-        </is>
-      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>69</v>
+      </c>
+      <c r="E26" t="n">
+        <v>89</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E27" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Deutschland Cup (Eishockey)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Deutschland Cup (Eishockey)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="n">
-        <v>79</v>
-      </c>
-      <c r="E27" t="n">
-        <v>99</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>VALVE WORLD EXPO 2026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="F28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Karnevalsauftakt 11.11.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>79</v>
-      </c>
-      <c r="E29" t="n">
-        <v>99</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="E29" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
+        <v>69</v>
+      </c>
+      <c r="E31" t="n">
+        <v>89</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>79</v>
+      </c>
+      <c r="E32" t="n">
         <v>99</v>
       </c>
-      <c r="E31" t="n">
-        <v>119</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>MEDICA + COMPAMED 2026</t>
-        </is>
-      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>209</v>
+        <v>99</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>219</v>
+        <v>119</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>MEDICA + COMPAMED 2026</t>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="E34" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>139</v>
-      </c>
       <c r="F34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>MEDICA + COMPAMED 2026 + Tokio Hotel (Konzert)</t>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-21</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>59</v>
+      </c>
+      <c r="E35" t="n">
+        <v>79</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
         <v>69</v>
@@ -1423,16 +1427,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>79</v>
@@ -1448,683 +1452,334 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E39" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="F38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-11-29</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-11-29</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>59</v>
+      </c>
+      <c r="E40" t="n">
+        <v>79</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
         <v>69</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E41" t="n">
         <v>89</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-03</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>VALVE WORLD EXPO 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Weihnachten – Familienbesuche</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Weihnachten – Familienbesuche</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E44" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>59</v>
-      </c>
-      <c r="E43" t="n">
-        <v>79</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" t="n">
-        <v>69</v>
-      </c>
-      <c r="E44" t="n">
-        <v>89</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="F44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026 + Broilers – Santa's Action Club + Weihnachten – Familienbesuche</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>79</v>
-      </c>
-      <c r="E45" t="n">
-        <v>99</v>
-      </c>
-      <c r="F45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026 + Weihnachten – Familienbesuche</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Weihnachten – Familienbesuche</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>69</v>
+      </c>
+      <c r="E47" t="n">
+        <v>89</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E48" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-12</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-12</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>59</v>
-      </c>
-      <c r="E48" t="n">
-        <v>79</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="F48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Silvester</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" t="n">
-        <v>69</v>
-      </c>
-      <c r="E49" t="n">
-        <v>89</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="n">
-        <v>79</v>
-      </c>
-      <c r="E50" t="n">
-        <v>99</v>
-      </c>
-      <c r="F50" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-19</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-19</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-12-20</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-12-20</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="n">
-        <v>59</v>
-      </c>
-      <c r="E53" t="n">
-        <v>79</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="n">
-        <v>69</v>
-      </c>
-      <c r="E54" t="n">
-        <v>89</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-22</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Weihnachten – Familienbesuche</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-24</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-24</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Weihnachten – Familienbesuche</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-25</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-25</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026 + Broilers – Santa's Action Club + Weihnachten – Familienbesuche</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-26</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-26</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="E58" s="2" t="n">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="F58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026 + Weihnachten – Familienbesuche</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-27</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-28</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Weihnachten – Familienbesuche</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>69</v>
-      </c>
-      <c r="E60" t="n">
-        <v>89</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Silvester</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="E62" s="2" t="n">
+      <c r="E49" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="F62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="F49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Silvester</t>
         </is>
@@ -5864,12 +5519,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Saison 1.08; Wochentag 1.12; Schulferien NRW (-3%); Nachfrageindex 1.17</t>
+          <t>Saison 1.08; Wochentag 1.12; Schulferien NRW (-3%); Nachfrageindex 1.17; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -5901,12 +5556,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Saison 1.08; Wochentag 1.15; Vorabend Allerheiligen (+3%); Schulferien NRW (-3%); Nachfrageindex 1.28</t>
+          <t>Saison 1.08; Wochentag 1.15; Vorabend Allerheiligen (+3%); Schulferien NRW (-3%); Nachfrageindex 1.28; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -5938,12 +5593,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 0.88; Allerheiligen (+0%); Nachfrageindex 0.88</t>
+          <t>Saison 1.00; Wochentag 0.88; Allerheiligen (+0%); Nachfrageindex 0.88; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -5975,12 +5630,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 0.95; Nachfrageindex 0.95</t>
+          <t>Saison 1.00; Wochentag 0.95; Nachfrageindex 0.95; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6012,12 +5667,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 0.97; Nachfrageindex 0.97</t>
+          <t>Saison 1.00; Wochentag 0.97; Nachfrageindex 0.97; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6049,12 +5704,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 0.97; Nachfrageindex 0.97</t>
+          <t>Saison 1.00; Wochentag 0.97; Nachfrageindex 0.97; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6090,12 +5745,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.00; Event: Deutschland Cup (Eishockey) (+5%); Nachfrageindex 1.05</t>
+          <t>Saison 1.00; Wochentag 1.00; Event: Deutschland Cup (Eishockey) (+5%); Nachfrageindex 1.05; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6131,12 +5786,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.12; Event: Deutschland Cup (Eishockey) (+5%); Nachfrageindex 1.18</t>
+          <t>Saison 1.00; Wochentag 1.12; Event: Deutschland Cup (Eishockey) (+5%); Nachfrageindex 1.18; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6172,12 +5827,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.15; Event: Deutschland Cup (Eishockey) (+5%); Nachfrageindex 1.21</t>
+          <t>Saison 1.00; Wochentag 1.15; Event: Deutschland Cup (Eishockey) (+5%); Nachfrageindex 1.21; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6213,12 +5868,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 0.88; Event: Deutschland Cup (Eishockey) (+5%); Nachfrageindex 0.92</t>
+          <t>Saison 1.00; Wochentag 0.88; Event: Deutschland Cup (Eishockey) (+5%); Nachfrageindex 0.92; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6250,12 +5905,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 0.95; Nachfrageindex 0.95</t>
+          <t>Saison 1.00; Wochentag 0.95; Nachfrageindex 0.95; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6287,12 +5942,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 0.97; Nachfrageindex 0.97</t>
+          <t>Saison 1.00; Wochentag 0.97; Nachfrageindex 0.97; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6328,12 +5983,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 0.97; Event: Karnevalsauftakt 11.11. (+12%); Nachfrageindex 1.09</t>
+          <t>Saison 1.00; Wochentag 0.97; Event: Karnevalsauftakt 11.11. (+12%); Nachfrageindex 1.09; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6020,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.00; Nachfrageindex 1.00</t>
+          <t>Saison 1.00; Wochentag 1.00; Nachfrageindex 1.00; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6402,12 +6057,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.12; Nachfrageindex 1.12</t>
+          <t>Saison 1.00; Wochentag 1.12; Nachfrageindex 1.12; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6094,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.15; Nachfrageindex 1.15</t>
+          <t>Saison 1.00; Wochentag 1.15; Nachfrageindex 1.15; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6480,12 +6135,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.00; Event: MEDICA + COMPAMED 2026 (+96%); Nachfrageindex 1.96</t>
+          <t>Saison 1.00; Wochentag 1.00; Event: MEDICA + COMPAMED 2026 (+96%); Nachfrageindex 1.96; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6176,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>freigeben</t>
+          <t>blockiert</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.00; Event: MEDICA + COMPAMED 2026 (+120%); Nachfrageindex 2.20</t>
+          <t>Saison 1.00; Wochentag 1.00; Event: MEDICA + COMPAMED 2026 (+120%); Nachfrageindex 2.20; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
         </is>
       </c>
     </row>
@@ -14147,13 +13802,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1207</v>
+        <v>1113</v>
       </c>
       <c r="E4" t="n">
-        <v>1073</v>
+        <v>990</v>
       </c>
     </row>
     <row r="5">
@@ -14168,13 +13823,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1435</v>
+        <v>716</v>
       </c>
       <c r="E5" t="n">
-        <v>1276</v>
+        <v>636</v>
       </c>
     </row>
     <row r="6">
@@ -14399,13 +14054,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>78.3</v>
+        <v>71.8</v>
       </c>
       <c r="D16" t="n">
-        <v>9193</v>
+        <v>8380</v>
       </c>
       <c r="E16" t="n">
-        <v>8172</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="17">
@@ -14420,13 +14075,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="D17" t="n">
-        <v>1725</v>
+        <v>1590</v>
       </c>
       <c r="E17" t="n">
-        <v>1533</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="18">
@@ -14441,13 +14096,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.6</v>
+        <v>7.5</v>
       </c>
       <c r="D18" t="n">
-        <v>2050</v>
+        <v>1023</v>
       </c>
       <c r="E18" t="n">
-        <v>1822</v>
+        <v>909</v>
       </c>
     </row>
     <row r="19">
@@ -14672,13 +14327,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>111.8</v>
+        <v>102.6</v>
       </c>
       <c r="D29" t="n">
-        <v>13132</v>
+        <v>11971</v>
       </c>
       <c r="E29" t="n">
-        <v>11675</v>
+        <v>10642</v>
       </c>
     </row>
     <row r="30">
@@ -14693,13 +14348,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.1</v>
+        <v>15.7</v>
       </c>
       <c r="D30" t="n">
-        <v>2156</v>
+        <v>1988</v>
       </c>
       <c r="E30" t="n">
-        <v>1917</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="31">
@@ -14714,13 +14369,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="D31" t="n">
-        <v>2466</v>
+        <v>1229</v>
       </c>
       <c r="E31" t="n">
-        <v>2193</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="32">
@@ -14945,13 +14600,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>139.4</v>
+        <v>128</v>
       </c>
       <c r="D42" t="n">
-        <v>16320</v>
+        <v>14915</v>
       </c>
       <c r="E42" t="n">
-        <v>14508</v>
+        <v>13259</v>
       </c>
     </row>
     <row r="43"/>

--- a/airbnb-pricing/output/preisplan.xlsx
+++ b/airbnb-pricing/output/preisplan.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -966,22 +966,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>3</v>
@@ -995,296 +995,300 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>MEDICA + COMPAMED 2026 + Tokio Hotel (Konzert)</t>
+          <t>MEDICA + COMPAMED 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>MEDICA + COMPAMED 2026 + Tokio Hotel (Konzert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2" t="n">
+      <c r="C23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E23" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>69</v>
-      </c>
-      <c r="E23" t="n">
-        <v>89</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>69</v>
+      </c>
+      <c r="E24" t="n">
+        <v>89</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C25" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D25" t="n">
         <v>79</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>99</v>
       </c>
-      <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-11-27</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>2026-11-28</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2" t="n">
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E26" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>69</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>89</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-03</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>VALVE WORLD EXPO 2026</t>
-        </is>
-      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E28" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>119</v>
-      </c>
       <c r="F28" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+          <t>VALVE WORLD EXPO 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2" t="n">
+      <c r="C30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E30" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="F29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>59</v>
-      </c>
-      <c r="E30" t="n">
-        <v>79</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -1294,130 +1298,130 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>69</v>
+      </c>
+      <c r="E32" t="n">
+        <v>89</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>2026-12-10</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-12-10</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
         <v>79</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E33" t="n">
         <v>99</v>
       </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>2026-12-12</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>2026-12-12</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="2" t="n">
+      <c r="C35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E35" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>59</v>
-      </c>
-      <c r="E35" t="n">
-        <v>79</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -1427,184 +1431,180 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>69</v>
+      </c>
+      <c r="E37" t="n">
+        <v>89</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
         <v>79</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E38" t="n">
         <v>99</v>
       </c>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>2026-12-19</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>2026-12-19</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2" t="n">
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E40" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="F39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-12-20</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-12-20</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>59</v>
-      </c>
-      <c r="E40" t="n">
-        <v>79</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>59</v>
+      </c>
+      <c r="E41" t="n">
+        <v>79</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>2026-12-21</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-12-21</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
         <v>69</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E42" t="n">
         <v>89</v>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-22</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Weihnachten – Familienbesuche</t>
-        </is>
-      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>2</v>
@@ -1618,168 +1618,197 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>109</v>
-      </c>
       <c r="F44" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026 + Broilers – Santa's Action Club + Weihnachten – Familienbesuche</t>
+          <t>Weihnachten – Familienbesuche</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026 + Weihnachten – Familienbesuche</t>
+          <t>Düsseldorfer Weihnachtsmarkt 2026 + Broilers – Santa's Action Club + Weihnachten – Familienbesuche</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026 + Weihnachten – Familienbesuche</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>2026-12-27</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>2026-12-28</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" s="2" t="n">
+      <c r="C47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E47" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Weihnachten – Familienbesuche</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2026-12-29</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2026-12-29</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
         <v>69</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E48" t="n">
         <v>89</v>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Silvester</t>
-        </is>
-      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Silvester</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="2" t="n">
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E50" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="F49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Silvester</t>
         </is>
@@ -6135,12 +6164,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>blockiert</t>
+          <t>freigeben</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.00; Event: MEDICA + COMPAMED 2026 (+96%); Nachfrageindex 1.96; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
+          <t>Saison 1.00; Wochentag 1.00; Event: MEDICA + COMPAMED 2026 (+96%); Nachfrageindex 1.96</t>
         </is>
       </c>
     </row>
@@ -6176,12 +6205,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>blockiert</t>
+          <t>freigeben</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Saison 1.00; Wochentag 1.00; Event: MEDICA + COMPAMED 2026 (+120%); Nachfrageindex 2.20; blockiert (Urlaub) – nur als Gesamtzeitraum vermietbar</t>
+          <t>Saison 1.00; Wochentag 1.00; Event: MEDICA + COMPAMED 2026 (+120%); Nachfrageindex 2.20</t>
         </is>
       </c>
     </row>
@@ -13823,13 +13852,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="D5" t="n">
-        <v>716</v>
+        <v>962</v>
       </c>
       <c r="E5" t="n">
-        <v>636</v>
+        <v>855</v>
       </c>
     </row>
     <row r="6">
@@ -14054,13 +14083,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>71.8</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>8380</v>
+        <v>8626</v>
       </c>
       <c r="E16" t="n">
-        <v>7450</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="17">
@@ -14096,13 +14125,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>1023</v>
+        <v>1375</v>
       </c>
       <c r="E18" t="n">
-        <v>909</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="19">
@@ -14327,13 +14356,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>102.6</v>
+        <v>104.2</v>
       </c>
       <c r="D29" t="n">
-        <v>11971</v>
+        <v>12323</v>
       </c>
       <c r="E29" t="n">
-        <v>10642</v>
+        <v>10955</v>
       </c>
     </row>
     <row r="30">
@@ -14369,13 +14398,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>1229</v>
+        <v>1622</v>
       </c>
       <c r="E31" t="n">
-        <v>1093</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="32">
@@ -14600,13 +14629,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>128</v>
+        <v>129.9</v>
       </c>
       <c r="D42" t="n">
-        <v>14915</v>
+        <v>15308</v>
       </c>
       <c r="E42" t="n">
-        <v>13259</v>
+        <v>13609</v>
       </c>
     </row>
     <row r="43"/>

--- a/airbnb-pricing/output/preisplan.xlsx
+++ b/airbnb-pricing/output/preisplan.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E8" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -754,10 +754,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -875,11 +875,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>109</v>
@@ -897,29 +897,29 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+          <t>belegt: Vergleichs-Median 132 € (inkl. allem)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>2</v>
@@ -938,12 +938,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -960,40 +960,44 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>glasstec 2026</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>Dimash Qudaibergen (Konzert)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>69</v>
-      </c>
-      <c r="E17" t="n">
-        <v>89</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -1002,25 +1006,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E18" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
@@ -1032,16 +1036,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
         <v>79</v>
@@ -1050,68 +1054,64 @@
         <v>99</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>79</v>
+      </c>
+      <c r="E20" t="n">
+        <v>99</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>belegt: Vergleichs-Median 96 € (inkl. allem)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>MEDICA + COMPAMED 2026</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>3</v>
@@ -1130,16 +1130,16 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>209</v>
@@ -1157,137 +1157,141 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>belegt: Vergleichs-Median 232 € (inkl. allem)</t>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>MEDICA + COMPAMED 2026 + Tokio Hotel (Konzert)</t>
+          <t>MEDICA + COMPAMED 2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+          <t>belegt: Vergleichs-Median 232 € (inkl. allem)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+          <t>MEDICA + COMPAMED 2026 + Tokio Hotel (Konzert)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>2026-11-21</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="2" t="n">
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E26" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>69</v>
-      </c>
-      <c r="E26" t="n">
-        <v>89</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -1296,25 +1300,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E27" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
@@ -1324,34 +1328,30 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>79</v>
+      </c>
+      <c r="E28" t="n">
+        <v>99</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -1360,96 +1360,96 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>2026-11-28</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>2026-11-28</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2" t="n">
+      <c r="C30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E30" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="F29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
         <v>69</v>
       </c>
-      <c r="E30" t="n">
-        <v>89</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-03</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>VALVE WORLD EXPO 2026</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="E31" t="n">
+        <v>89</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -1458,62 +1458,66 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>VALVE WORLD EXPO 2026</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E32" s="2" t="n">
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E33" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" t="n">
-        <v>69</v>
-      </c>
-      <c r="E33" t="n">
-        <v>89</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -1522,25 +1526,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E34" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
@@ -1550,64 +1554,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>79</v>
+      </c>
+      <c r="E35" t="n">
+        <v>99</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>2026-12-12</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E35" s="2" t="n">
+      <c r="C36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E36" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="F35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" t="n">
-        <v>69</v>
-      </c>
-      <c r="E36" t="n">
-        <v>89</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -1616,25 +1620,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E37" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
@@ -1644,98 +1648,94 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>79</v>
+      </c>
+      <c r="E38" t="n">
+        <v>99</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2026-12-18</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>2026-12-19</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E38" s="2" t="n">
+      <c r="C39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E39" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="F38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Düsseldorfer Weihnachtsmarkt 2026</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2026-12-20</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2026-12-21</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
         <v>69</v>
       </c>
-      <c r="E39" t="n">
-        <v>89</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-22</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Weihnachten – Familienbesuche</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="E40" t="n">
+        <v>89</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -1744,22 +1744,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>2</v>
@@ -1778,29 +1778,29 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026 + Weihnachten – Familienbesuche + Broilers – Santa's Action Club</t>
+          <t>Weihnachten – Familienbesuche</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1812,29 +1812,29 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E43" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>119</v>
-      </c>
       <c r="F43" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Düsseldorfer Weihnachtsmarkt 2026 + Weihnachten – Familienbesuche</t>
+          <t>Düsseldorfer Weihnachtsmarkt 2026 + Weihnachten – Familienbesuche + Broilers – Santa's Action Club</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1846,130 +1846,164 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Düsseldorfer Weihnachtsmarkt 2026 + Weihnachten – Familienbesuche</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>2026-12-27</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>2026-12-28</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" s="2" t="n">
+      <c r="C45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Weihnachten – Familienbesuche</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026-12-29</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2026-12-29</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
         <v>69</v>
       </c>
-      <c r="E45" t="n">
-        <v>89</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Silvester</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+      <c r="E46" t="n">
+        <v>89</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Silvester</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2" t="n">
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E48" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="F47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Silvester</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
@@ -1986,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2430,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -2593,17 +2627,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2027-04-10</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>2</v>
@@ -2622,154 +2656,150 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2027-04-10</t>
+          <t>2027-04-11</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2027-04-10</t>
+          <t>2027-04-11</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>BEAUTY DÜSSELDORF + TOP HAIR 2027 + FIBO 2027 (Köln)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>99</v>
+      </c>
+      <c r="E20" t="n">
+        <v>119</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2027-05-22</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2027-05-22</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E21" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>BEAUTY DÜSSELDORF + TOP HAIR 2027 + FIBO 2027 (Köln)</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Japan-Tag Düsseldorf/NRW 2027</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2027-04-11</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>2027-04-11</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>BEAUTY DÜSSELDORF + TOP HAIR 2027 + FIBO 2027 (Köln)</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>99</v>
-      </c>
-      <c r="E21" t="n">
-        <v>119</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2027-05-22</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>2027-05-22</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Japan-Tag Düsseldorf/NRW 2027</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2027-06-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2027-06-03</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>89</v>
+      </c>
+      <c r="E22" t="n">
+        <v>109</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2027-06-01</t>
+          <t>2027-06-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2027-06-03</t>
+          <t>2027-06-05</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E23" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -2784,25 +2814,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
+          <t>2027-06-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2027-06-06</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="E24" t="n">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
@@ -2814,25 +2844,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2027-06-06</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2027-06-06</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
@@ -2844,22 +2874,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2027-06-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2027-06-10</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E26" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2874,22 +2904,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2027-06-08</t>
+          <t>2027-06-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2027-06-10</t>
+          <t>2027-06-12</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E27" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
@@ -2904,25 +2934,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2027-06-11</t>
+          <t>2027-06-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2027-06-12</t>
+          <t>2027-06-13</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="E28" t="n">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
@@ -2934,25 +2964,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2027-06-13</t>
+          <t>2027-06-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2027-06-13</t>
+          <t>2027-06-14</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E29" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
@@ -2964,22 +2994,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2027-06-14</t>
+          <t>2027-06-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2027-06-14</t>
+          <t>2027-06-17</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E30" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F30" t="n">
         <v>2</v>
@@ -2994,22 +3024,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2027-06-15</t>
+          <t>2027-06-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2027-06-19</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E31" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
@@ -3022,54 +3052,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2027-06-18</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2027-06-19</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" t="n">
-        <v>99</v>
-      </c>
-      <c r="E32" t="n">
-        <v>119</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>GIFA / METEC / THERMPROCESS / NEWCAST 2027</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2027-06-20</t>
+          <t>2027-06-21</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2027-06-20</t>
+          <t>2027-06-24</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>2</v>
@@ -3088,22 +3122,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2027-06-21</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2027-06-24</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>2</v>
@@ -3120,61 +3154,57 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>GIFA / METEC / THERMPROCESS / NEWCAST 2027</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2027-06-26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2027-06-26</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>99</v>
+      </c>
+      <c r="E35" t="n">
+        <v>119</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2027-06-26</t>
+          <t>2027-06-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2027-06-26</t>
+          <t>2027-06-27</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="E36" t="n">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
@@ -3186,25 +3216,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2027-06-27</t>
+          <t>2027-06-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2027-06-27</t>
+          <t>2027-06-28</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E37" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
@@ -3216,22 +3246,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2027-06-28</t>
+          <t>2027-06-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2027-06-28</t>
+          <t>2027-06-30</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E38" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F38" t="n">
         <v>2</v>
@@ -3244,30 +3274,34 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2027-06-29</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2027-06-30</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>89</v>
-      </c>
-      <c r="E39" t="n">
-        <v>109</v>
-      </c>
-      <c r="F39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-01</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-01</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Cologne Pride / CSD (Köln)</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -3276,22 +3310,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2027-07-01</t>
+          <t>2027-07-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2027-07-01</t>
+          <t>2027-07-02</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>2</v>
@@ -3310,57 +3344,57 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2027-07-02</t>
+          <t>2027-07-03</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2027-07-02</t>
+          <t>2027-07-03</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Cologne Pride / CSD (Köln)</t>
+          <t>Die Toten Hosen (Stadion) + Cologne Pride / CSD (Köln)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2027-07-03</t>
+          <t>2027-07-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2027-07-03</t>
+          <t>2027-07-04</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="E42" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>179</v>
-      </c>
       <c r="F42" s="2" t="n">
         <v>2</v>
       </c>
@@ -3376,61 +3410,57 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-04</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-04</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Die Toten Hosen (Stadion) + Cologne Pride / CSD (Köln)</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2027-07-08</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>69</v>
+      </c>
+      <c r="E43" t="n">
+        <v>89</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2027-07-05</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2027-07-08</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E44" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
@@ -3440,189 +3470,193 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>79</v>
-      </c>
-      <c r="E45" t="n">
-        <v>99</v>
-      </c>
-      <c r="F45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-10</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-10</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Die Toten Hosen (Stadion)</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-10</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-10</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2" t="n">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2027-07-11</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2027-07-15</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>69</v>
+      </c>
+      <c r="E46" t="n">
+        <v>89</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Rheinkirmes 2027</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-17</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-17</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="E48" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Die Toten Hosen (Stadion)</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Rheinkirmes 2027 + Karol G (Stadion)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2027-07-11</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2027-07-11</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="n">
-        <v>59</v>
-      </c>
-      <c r="E47" t="n">
-        <v>79</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2027-07-12</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2027-07-15</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>4</v>
-      </c>
-      <c r="D48" t="n">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2027-07-18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2027-07-22</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="n">
         <v>69</v>
       </c>
-      <c r="E48" t="n">
-        <v>89</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-16</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-16</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Rheinkirmes 2027</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+      <c r="E49" t="n">
+        <v>89</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2027-07-17</t>
+          <t>2027-07-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2027-07-17</t>
+          <t>2027-07-24</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="E50" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>149</v>
-      </c>
       <c r="F50" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Rheinkirmes 2027 + Karol G (Stadion)</t>
+          <t>Rheinkirmes 2027</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3634,22 +3668,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
+          <t>2027-07-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
+          <t>2027-07-29</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E51" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -3664,25 +3698,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2027-07-19</t>
+          <t>2027-07-30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2027-07-22</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E52" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
@@ -3692,61 +3726,57 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-23</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-24</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Rheinkirmes 2027</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2027-08-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2027-08-05</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="n">
+        <v>69</v>
+      </c>
+      <c r="E53" t="n">
+        <v>89</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2027-07-25</t>
+          <t>2027-08-06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2027-07-25</t>
+          <t>2027-08-07</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E54" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
@@ -3758,16 +3788,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2027-07-26</t>
+          <t>2027-08-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2027-07-29</t>
+          <t>2027-08-12</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
         <v>69</v>
@@ -3788,12 +3818,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2027-07-30</t>
+          <t>2027-08-13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2027-08-14</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3818,22 +3848,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2027-08-01</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2027-08-01</t>
+          <t>2027-08-19</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E57" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -3848,25 +3878,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2027-08-02</t>
+          <t>2027-08-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2027-08-05</t>
+          <t>2027-08-21</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E58" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
@@ -3878,25 +3908,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2027-08-06</t>
+          <t>2027-08-22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2027-08-07</t>
+          <t>2027-08-23</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E59" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
@@ -3906,641 +3936,641 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2027-08-08</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2027-08-08</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>59</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-24</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-25</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
+      <c r="E60" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>gamescom 2027 (Köln)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2027-08-09</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2027-08-12</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>4</v>
-      </c>
-      <c r="D61" t="n">
-        <v>69</v>
-      </c>
-      <c r="E61" t="n">
-        <v>89</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>CARAVAN SALON 2027 + gamescom 2027 (Köln)</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2027-08-13</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2027-08-14</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>2</v>
-      </c>
-      <c r="D62" t="n">
-        <v>79</v>
-      </c>
-      <c r="E62" t="n">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-27</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-27</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>CARAVAN SALON 2027 + gamescom 2027 (Köln) + Neusser Bürger-Schützenfest 2027</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-28</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-28</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>CARAVAN SALON 2027 + gamescom 2027 (Köln) + Neusser Bürger-Schützenfest 2027</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-29</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-29</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>CARAVAN SALON 2027 + Neusser Bürger-Schützenfest 2027 + gamescom 2027 (Köln)</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-30</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-31</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="F62" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2027-08-15</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2027-08-15</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>59</v>
-      </c>
-      <c r="E63" t="n">
-        <v>79</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2027-08-16</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2027-08-19</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>4</v>
-      </c>
-      <c r="D64" t="n">
-        <v>69</v>
-      </c>
-      <c r="E64" t="n">
-        <v>89</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2027-08-20</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2027-08-21</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>2</v>
-      </c>
-      <c r="D65" t="n">
-        <v>79</v>
-      </c>
-      <c r="E65" t="n">
-        <v>99</v>
-      </c>
-      <c r="F65" t="n">
-        <v>2</v>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+      <c r="E65" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>CARAVAN SALON 2027 + Neusser Bürger-Schützenfest 2027</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2027-08-22</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2027-08-22</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="n">
-        <v>59</v>
-      </c>
-      <c r="E66" t="n">
-        <v>79</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>CARAVAN SALON 2027</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2027-08-23</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2027-08-23</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="n">
-        <v>69</v>
-      </c>
-      <c r="E67" t="n">
-        <v>89</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2027-09-02</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2027-09-02</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>CARAVAN SALON 2027</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2027-08-24</t>
+          <t>2027-09-03</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>2027-08-25</t>
+          <t>2027-09-04</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>gamescom 2027 (Köln)</t>
+          <t>CARAVAN SALON 2027</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t>2027-09-05</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t>2027-09-05</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D69" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>CARAVAN SALON 2027</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2027-09-06</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2027-09-09</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>89</v>
+      </c>
+      <c r="E70" t="n">
+        <v>109</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2027-09-11</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="n">
         <v>99</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E71" t="n">
         <v>119</v>
       </c>
-      <c r="F69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027 + gamescom 2027 (Köln)</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-27</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-27</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="2" t="n">
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2027-09-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2027-09-12</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>69</v>
+      </c>
+      <c r="E72" t="n">
+        <v>89</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2027-09-13</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2027-09-16</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" t="n">
+        <v>89</v>
+      </c>
+      <c r="E73" t="n">
         <v>109</v>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027 + gamescom 2027 (Köln) + Neusser Bürger-Schützenfest 2027</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-28</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-28</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="2" t="n">
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2027-09-18</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="n">
+        <v>99</v>
+      </c>
+      <c r="E74" t="n">
         <v>119</v>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027 + gamescom 2027 (Köln) + Neusser Bürger-Schützenfest 2027</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-29</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-29</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E72" s="2" t="n">
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2027-09-19</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2027-09-19</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>69</v>
+      </c>
+      <c r="E75" t="n">
+        <v>89</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2027-09-20</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2027-09-20</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>89</v>
+      </c>
+      <c r="E76" t="n">
         <v>109</v>
       </c>
-      <c r="F72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027 + Neusser Bürger-Schützenfest 2027 + gamescom 2027 (Köln)</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-30</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-30</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027 + Neusser Bürger-Schützenfest 2027</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-31</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>2027-08-31</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027 + Neusser Bürger-Schützenfest 2027</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>2027-09-01</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>2027-09-01</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>2027-09-02</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>2027-09-02</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2027-09-03</t>
+          <t>2027-09-21</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>2027-09-04</t>
+          <t>2027-09-23</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>CARAVAN SALON 2027</t>
+          <t>DMEXCO 2027 (Köln)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>2027-09-05</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>2027-09-05</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>CARAVAN SALON 2027</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2027-09-24</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2027-09-25</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>99</v>
+      </c>
+      <c r="E78" t="n">
+        <v>119</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2027-09-06</t>
+          <t>2027-09-26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2027-09-09</t>
+          <t>2027-09-26</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E79" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
@@ -4552,22 +4582,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2027-09-10</t>
+          <t>2027-09-27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2027-09-11</t>
+          <t>2027-09-29</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E80" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -4582,302 +4612,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2027-09-12</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2027-09-12</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E81" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2027-09-13</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2027-09-16</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>4</v>
-      </c>
-      <c r="D82" t="n">
-        <v>89</v>
-      </c>
-      <c r="E82" t="n">
-        <v>109</v>
-      </c>
-      <c r="F82" t="n">
-        <v>2</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2027-09-17</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2027-09-18</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>2</v>
-      </c>
-      <c r="D83" t="n">
-        <v>99</v>
-      </c>
-      <c r="E83" t="n">
-        <v>119</v>
-      </c>
-      <c r="F83" t="n">
-        <v>2</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2027-09-19</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2027-09-19</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="n">
-        <v>69</v>
-      </c>
-      <c r="E84" t="n">
-        <v>89</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2027-09-20</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2027-09-20</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="n">
-        <v>89</v>
-      </c>
-      <c r="E85" t="n">
-        <v>109</v>
-      </c>
-      <c r="F85" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>2027-09-21</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>2027-09-23</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>DMEXCO 2027 (Köln)</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2027-09-24</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2027-09-25</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>2</v>
-      </c>
-      <c r="D87" t="n">
-        <v>99</v>
-      </c>
-      <c r="E87" t="n">
-        <v>119</v>
-      </c>
-      <c r="F87" t="n">
-        <v>2</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2027-09-26</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2027-09-26</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="n">
-        <v>69</v>
-      </c>
-      <c r="E88" t="n">
-        <v>89</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2027-09-27</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2027-09-29</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" t="n">
-        <v>89</v>
-      </c>
-      <c r="E89" t="n">
-        <v>109</v>
-      </c>
-      <c r="F89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2027-09-30</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2027-09-30</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="n">
-        <v>89</v>
-      </c>
-      <c r="E90" t="n">
-        <v>109</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
         <is>
           <t>abgeleitet: Vergleichspreise normaler Tage + eigene Buchungen</t>
         </is>
@@ -5409,10 +5165,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -5497,10 +5253,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D14" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -5693,7 +5449,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+          <t>belegt: Vergleichs-Median 132 € (inkl. allem)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5739,7 +5495,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Annahme: Event-Aufschlag ohne Vergleichspreise</t>
+          <t>belegt: Vergleichs-Median 132 € (inkl. allem)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9659,10 +9415,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
@@ -9935,10 +9691,10 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>2</v>
@@ -11189,10 +10945,10 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>2</v>
@@ -11885,10 +11641,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D68" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -12187,10 +11943,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D75" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -12489,10 +12245,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D82" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -12783,10 +12539,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D89" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -13077,10 +12833,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D96" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
@@ -13371,10 +13127,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D103" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -13665,10 +13421,10 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D110" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
@@ -14025,10 +13781,10 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>2</v>
@@ -15476,10 +15232,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="E4" t="n">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5">
@@ -15497,10 +15253,10 @@
         <v>6.4</v>
       </c>
       <c r="D5" t="n">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E5" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6">
@@ -15518,10 +15274,10 @@
         <v>8.6</v>
       </c>
       <c r="D6" t="n">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E6" t="n">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="7">
@@ -15539,10 +15295,10 @@
         <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E7" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8">
@@ -15560,10 +15316,10 @@
         <v>2.7</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E8" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -15581,10 +15337,10 @@
         <v>1.9</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E9" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -15602,7 +15358,7 @@
         <v>1.7</v>
       </c>
       <c r="D10" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E10" t="n">
         <v>194</v>
@@ -15644,10 +15400,10 @@
         <v>10.6</v>
       </c>
       <c r="D12" t="n">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="13">
@@ -15665,10 +15421,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E13" t="n">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14">
@@ -15686,10 +15442,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="E14" t="n">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15">
@@ -15707,10 +15463,10 @@
         <v>10.2</v>
       </c>
       <c r="D15" t="n">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="E15" t="n">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="16">
@@ -15728,10 +15484,10 @@
         <v>71.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>8270</v>
+        <v>8301</v>
       </c>
       <c r="E16" t="n">
-        <v>7352</v>
+        <v>7380</v>
       </c>
     </row>
     <row r="17">
@@ -15749,10 +15505,10 @@
         <v>11.6</v>
       </c>
       <c r="D17" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="E17" t="n">
-        <v>1207</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="18">
@@ -15770,10 +15526,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="E18" t="n">
-        <v>1210</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="19">
@@ -15791,10 +15547,10 @@
         <v>12.3</v>
       </c>
       <c r="D19" t="n">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="E19" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="20">
@@ -15812,10 +15568,10 @@
         <v>4.9</v>
       </c>
       <c r="D20" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E20" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21">
@@ -15833,10 +15589,10 @@
         <v>3.8</v>
       </c>
       <c r="D21" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E21" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22">
@@ -15854,10 +15610,10 @@
         <v>2.6</v>
       </c>
       <c r="D22" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E22" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23">
@@ -15875,10 +15631,10 @@
         <v>2.4</v>
       </c>
       <c r="D23" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E23" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24">
@@ -15896,10 +15652,10 @@
         <v>1.2</v>
       </c>
       <c r="D24" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E24" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25">
@@ -15917,10 +15673,10 @@
         <v>15.1</v>
       </c>
       <c r="D25" t="n">
-        <v>1780</v>
+        <v>1787</v>
       </c>
       <c r="E25" t="n">
-        <v>1583</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="26">
@@ -15938,10 +15694,10 @@
         <v>12.4</v>
       </c>
       <c r="D26" t="n">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="E26" t="n">
-        <v>1194</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="27">
@@ -15959,10 +15715,10 @@
         <v>11.9</v>
       </c>
       <c r="D27" t="n">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="E27" t="n">
-        <v>1028</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="28">
@@ -15980,10 +15736,10 @@
         <v>14.5</v>
       </c>
       <c r="D28" t="n">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="E28" t="n">
-        <v>1438</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="29">
@@ -16001,10 +15757,10 @@
         <v>101.9</v>
       </c>
       <c r="D29" t="n">
-        <v>11815</v>
+        <v>11859</v>
       </c>
       <c r="E29" t="n">
-        <v>10503</v>
+        <v>10543</v>
       </c>
     </row>
     <row r="30">
@@ -16022,10 +15778,10 @@
         <v>14.6</v>
       </c>
       <c r="D30" t="n">
-        <v>1698</v>
+        <v>1704</v>
       </c>
       <c r="E30" t="n">
-        <v>1509</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="31">
@@ -16043,10 +15799,10 @@
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>1604</v>
+        <v>1610</v>
       </c>
       <c r="E31" t="n">
-        <v>1426</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="32">
@@ -16064,10 +15820,10 @@
         <v>15.4</v>
       </c>
       <c r="D32" t="n">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="E32" t="n">
-        <v>1398</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="33">
@@ -16085,10 +15841,10 @@
         <v>6.1</v>
       </c>
       <c r="D33" t="n">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E33" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="34">
@@ -16106,10 +15862,10 @@
         <v>4.8</v>
       </c>
       <c r="D34" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E34" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="35">
@@ -16127,10 +15883,10 @@
         <v>3.3</v>
       </c>
       <c r="D35" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E35" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="36">
@@ -16148,10 +15904,10 @@
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E36" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37">
@@ -16169,7 +15925,7 @@
         <v>1.6</v>
       </c>
       <c r="D37" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E37" t="n">
         <v>181</v>
@@ -16190,10 +15946,10 @@
         <v>18.9</v>
       </c>
       <c r="D38" t="n">
-        <v>2226</v>
+        <v>2234</v>
       </c>
       <c r="E38" t="n">
-        <v>1979</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="39">
@@ -16211,10 +15967,10 @@
         <v>15.5</v>
       </c>
       <c r="D39" t="n">
-        <v>1678</v>
+        <v>1685</v>
       </c>
       <c r="E39" t="n">
-        <v>1492</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40">
@@ -16232,10 +15988,10 @@
         <v>14.9</v>
       </c>
       <c r="D40" t="n">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="E40" t="n">
-        <v>1285</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="41">
@@ -16253,10 +16009,10 @@
         <v>18.1</v>
       </c>
       <c r="D41" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="E41" t="n">
-        <v>1797</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="42">
@@ -16274,10 +16030,10 @@
         <v>127</v>
       </c>
       <c r="D42" t="n">
-        <v>14671</v>
+        <v>14726</v>
       </c>
       <c r="E42" t="n">
-        <v>13042</v>
+        <v>13091</v>
       </c>
     </row>
     <row r="43"/>
@@ -16315,10 +16071,10 @@
         <v>53.9</v>
       </c>
       <c r="D45" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E45" t="n">
-        <v>5242</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="46">
@@ -16335,7 +16091,7 @@
         <v>108</v>
       </c>
       <c r="E46" t="n">
-        <v>6512</v>
+        <v>6537</v>
       </c>
     </row>
     <row r="47">
@@ -16352,7 +16108,7 @@
         <v>116</v>
       </c>
       <c r="E47" t="n">
-        <v>9247</v>
+        <v>9282</v>
       </c>
     </row>
   </sheetData>

--- a/airbnb-pricing/output/preisplan.xlsx
+++ b/airbnb-pricing/output/preisplan.xlsx
@@ -15235,7 +15235,7 @@
         <v>954</v>
       </c>
       <c r="E4" t="n">
-        <v>848</v>
+        <v>778</v>
       </c>
     </row>
     <row r="5">
@@ -15256,7 +15256,7 @@
         <v>956</v>
       </c>
       <c r="E5" t="n">
-        <v>850</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6">
@@ -15277,7 +15277,7 @@
         <v>884</v>
       </c>
       <c r="E6" t="n">
-        <v>786</v>
+        <v>721</v>
       </c>
     </row>
     <row r="7">
@@ -15298,7 +15298,7 @@
         <v>376</v>
       </c>
       <c r="E7" t="n">
-        <v>334</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8">
@@ -15319,7 +15319,7 @@
         <v>374</v>
       </c>
       <c r="E8" t="n">
-        <v>333</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
@@ -15340,7 +15340,7 @@
         <v>280</v>
       </c>
       <c r="E9" t="n">
-        <v>249</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -15361,7 +15361,7 @@
         <v>219</v>
       </c>
       <c r="E10" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -15382,7 +15382,7 @@
         <v>114</v>
       </c>
       <c r="E11" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -15403,7 +15403,7 @@
         <v>1251</v>
       </c>
       <c r="E12" t="n">
-        <v>1112</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="13">
@@ -15424,7 +15424,7 @@
         <v>943</v>
       </c>
       <c r="E13" t="n">
-        <v>839</v>
+        <v>769</v>
       </c>
     </row>
     <row r="14">
@@ -15445,7 +15445,7 @@
         <v>812</v>
       </c>
       <c r="E14" t="n">
-        <v>722</v>
+        <v>663</v>
       </c>
     </row>
     <row r="15">
@@ -15466,7 +15466,7 @@
         <v>1137</v>
       </c>
       <c r="E15" t="n">
-        <v>1010</v>
+        <v>927</v>
       </c>
     </row>
     <row r="16">
@@ -15487,7 +15487,7 @@
         <v>8301</v>
       </c>
       <c r="E16" t="n">
-        <v>7380</v>
+        <v>6771</v>
       </c>
     </row>
     <row r="17">
@@ -15508,7 +15508,7 @@
         <v>1363</v>
       </c>
       <c r="E17" t="n">
-        <v>1212</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="18">
@@ -15529,7 +15529,7 @@
         <v>1366</v>
       </c>
       <c r="E18" t="n">
-        <v>1215</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="19">
@@ -15550,7 +15550,7 @@
         <v>1263</v>
       </c>
       <c r="E19" t="n">
-        <v>1123</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="20">
@@ -15571,7 +15571,7 @@
         <v>537</v>
       </c>
       <c r="E20" t="n">
-        <v>478</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21">
@@ -15592,7 +15592,7 @@
         <v>535</v>
       </c>
       <c r="E21" t="n">
-        <v>475</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22">
@@ -15613,7 +15613,7 @@
         <v>400</v>
       </c>
       <c r="E22" t="n">
-        <v>356</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23">
@@ -15634,7 +15634,7 @@
         <v>312</v>
       </c>
       <c r="E23" t="n">
-        <v>278</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24">
@@ -15655,7 +15655,7 @@
         <v>163</v>
       </c>
       <c r="E24" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25">
@@ -15676,7 +15676,7 @@
         <v>1787</v>
       </c>
       <c r="E25" t="n">
-        <v>1589</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="26">
@@ -15697,7 +15697,7 @@
         <v>1348</v>
       </c>
       <c r="E26" t="n">
-        <v>1198</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="27">
@@ -15718,7 +15718,7 @@
         <v>1160</v>
       </c>
       <c r="E27" t="n">
-        <v>1032</v>
+        <v>946</v>
       </c>
     </row>
     <row r="28">
@@ -15739,7 +15739,7 @@
         <v>1624</v>
       </c>
       <c r="E28" t="n">
-        <v>1443</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="29">
@@ -15760,7 +15760,7 @@
         <v>11859</v>
       </c>
       <c r="E29" t="n">
-        <v>10543</v>
+        <v>9672</v>
       </c>
     </row>
     <row r="30">
@@ -15781,7 +15781,7 @@
         <v>1704</v>
       </c>
       <c r="E30" t="n">
-        <v>1515</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="31">
@@ -15802,7 +15802,7 @@
         <v>1610</v>
       </c>
       <c r="E31" t="n">
-        <v>1431</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="32">
@@ -15823,7 +15823,7 @@
         <v>1579</v>
       </c>
       <c r="E32" t="n">
-        <v>1403</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="33">
@@ -15844,7 +15844,7 @@
         <v>672</v>
       </c>
       <c r="E33" t="n">
-        <v>597</v>
+        <v>548</v>
       </c>
     </row>
     <row r="34">
@@ -15865,7 +15865,7 @@
         <v>668</v>
       </c>
       <c r="E34" t="n">
-        <v>594</v>
+        <v>545</v>
       </c>
     </row>
     <row r="35">
@@ -15886,7 +15886,7 @@
         <v>500</v>
       </c>
       <c r="E35" t="n">
-        <v>445</v>
+        <v>408</v>
       </c>
     </row>
     <row r="36">
@@ -15907,7 +15907,7 @@
         <v>390</v>
       </c>
       <c r="E36" t="n">
-        <v>347</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37">
@@ -15928,7 +15928,7 @@
         <v>204</v>
       </c>
       <c r="E37" t="n">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38">
@@ -15949,7 +15949,7 @@
         <v>2234</v>
       </c>
       <c r="E38" t="n">
-        <v>1986</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="39">
@@ -15970,7 +15970,7 @@
         <v>1685</v>
       </c>
       <c r="E39" t="n">
-        <v>1498</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="40">
@@ -15991,7 +15991,7 @@
         <v>1451</v>
       </c>
       <c r="E40" t="n">
-        <v>1290</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="41">
@@ -16012,7 +16012,7 @@
         <v>2030</v>
       </c>
       <c r="E41" t="n">
-        <v>1804</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="42">
@@ -16033,7 +16033,7 @@
         <v>14726</v>
       </c>
       <c r="E42" t="n">
-        <v>13091</v>
+        <v>12011</v>
       </c>
     </row>
     <row r="43"/>
@@ -16074,7 +16074,7 @@
         <v>110</v>
       </c>
       <c r="E45" t="n">
-        <v>5262</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="46">
@@ -16091,7 +16091,7 @@
         <v>108</v>
       </c>
       <c r="E46" t="n">
-        <v>6537</v>
+        <v>5997</v>
       </c>
     </row>
     <row r="47">
@@ -16108,7 +16108,7 @@
         <v>116</v>
       </c>
       <c r="E47" t="n">
-        <v>9282</v>
+        <v>8515</v>
       </c>
     </row>
   </sheetData>
